--- a/MLOps/MLflow/demo/simple_train_test/runs_info.xlsx
+++ b/MLOps/MLflow/demo/simple_train_test/runs_info.xlsx
@@ -461,94 +461,94 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>metrics.system/system_memory_usage_megabytes</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/network_receive_megabytes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/network_transmit_megabytes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.val_MulticlassAccuracy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/disk_usage_megabytes</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.train_MulticlassAccuracy</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/gpu_0_memory_usage_percentage</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/gpu_0_power_usage_watts</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/cpu_utilization_percentage</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/gpu_0_utilization_percentage</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.train_loss</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/gpu_0_power_usage_percentage</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.val_loss</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/disk_usage_percentage</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/disk_available_megabytes</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>metrics.system/gpu_0_memory_usage_megabytes</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>metrics.train_MulticlassF1Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.val_MulticlassAccuracy</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/network_transmit_megabytes</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/gpu_0_memory_usage_percentage</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/system_memory_usage_megabytes</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.val_loss</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.train_MulticlassAccuracy</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/disk_available_megabytes</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/gpu_0_memory_usage_megabytes</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>metrics.val_MulticlassF1Score</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/gpu_0_power_usage_percentage</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/gpu_0_utilization_percentage</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/network_receive_megabytes</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/gpu_0_power_usage_watts</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/disk_usage_megabytes</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.train_loss</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/cpu_utilization_percentage</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>metrics.system/disk_usage_percentage</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>metrics.system/system_memory_usage_percentage</t>
@@ -556,62 +556,62 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>params.Batch size</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>params. Metric 1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>params.Epochs</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>params. Metric 0</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>params.Lr</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>params.Loss</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>params.Optimizer</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>params.Loss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>params. Metric 0</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>params.Epochs</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>params. Metric 1</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>params.Batch size</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>tags.mlflow.runName</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>tags.mlflow.source.type</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>tags.mlflow.runName</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>tags.mlflow.source.git.commit</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>tags.mlflow.source.name</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>tags.mlflow.log-model.history</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>tags.mlflow.source.git.commit</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>tags.mlflow.source.name</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -623,12 +623,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8dbb19b9d6364667b09c576acc910756</t>
+          <t>9fb8c045506549d8b61f455d93d705db</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>764618360763554814</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,134 +638,134 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mlflow-artifacts:/1/8dbb19b9d6364667b09c576acc910756/artifacts</t>
+          <t>file:///mnt/DATA/Local/Source/Python/semester_9/AIP391/Video_anomaly_detection/MLOps/MLflow/demo/simple_train_test/mlruns/764618360763554814/9fb8c045506549d8b61f455d93d705db/artifacts</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-01-21 21:02:36</t>
+          <t>2025-02-18 13:42:58</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-01-21 21:03:07</t>
+          <t>2025-02-18 13:43:35</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.1184000000357628</v>
+        <v>11572.4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1200714260339737</v>
+        <v>31.40975100000014</v>
       </c>
       <c r="I2" t="n">
-        <v>1.920797999999991</v>
+        <v>0.6356130000000064</v>
       </c>
       <c r="J2" t="n">
+        <v>0.953421413898468</v>
+      </c>
+      <c r="K2" t="n">
+        <v>547946</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9530174136161804</v>
+      </c>
+      <c r="M2" t="n">
         <v>5.8</v>
       </c>
-      <c r="K2" t="n">
-        <v>12418.4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.294981479644775</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1184000000357628</v>
-      </c>
       <c r="N2" t="n">
-        <v>376389.8</v>
+        <v>38.8</v>
       </c>
       <c r="O2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.07908183336257935</v>
+      </c>
+      <c r="R2" t="n">
+        <v>31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.06115603055804968</v>
+      </c>
+      <c r="T2" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>406751.2</v>
+      </c>
+      <c r="V2" t="n">
         <v>1002.6</v>
       </c>
-      <c r="P2" t="n">
-        <v>0.1200714260339737</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.872377</v>
-      </c>
-      <c r="T2" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="U2" t="n">
-        <v>578307.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.292442321777344</v>
-      </c>
       <c r="W2" t="n">
-        <v>4.3</v>
+        <v>0.9530174136161804</v>
       </c>
       <c r="X2" t="n">
-        <v>60.6</v>
+        <v>0.953421413898468</v>
       </c>
       <c r="Y2" t="n">
-        <v>18.5</v>
+        <v>17.2</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.0000000000000002e-06</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>MulticlassF1Score</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>MulticlassAccuracy</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>CrossEntropyLoss</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>Adam</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>CrossEntropyLoss</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>MulticlassAccuracy</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>MulticlassF1Score</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>run 0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
           <t>LOCAL</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>run 3</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[{"run_id": "8dbb19b9d6364667b09c576acc910756", "artifact_path": "model", "utc_time_created": "2025-01-21 14:03:04.079293", "model_uuid": "8650457768d44baf9b479f5a828bdb3f", "flavors": {"pytorch": {"model_data": "data", "pytorch_version": "2.5.1+cu124", "code": null}, "python_function": {"pickle_module_name": "mlflow.pytorch.pickle_module", "loader_module": "mlflow.pytorch", "python_version": "3.11.11", "data": "data", "env": {"conda": "conda.yaml", "virtualenv": "python_env.yaml"}}}}]</t>
+          <t>fe594eef254e816ae4543d2d9b17f31e24a11036</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>d54fd148a0dafb54d76453320abf53da0d6b9804</t>
+          <t>/home/trong/Downloads/Local/Source/Python/semester_9/AIP391/Video_anomaly_detection/MLOps/MLflow/demo/simple_train_test/main.py</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>/home/trong/Downloads/Local/Source/Python/semester_9/AIP391/Video_anomaly_detection/MLOps/MLflow/demo/train_test/main.py</t>
+          <t>[{"run_id": "9fb8c045506549d8b61f455d93d705db", "artifact_path": "model", "utc_time_created": "2025-02-18 06:43:32.275505", "model_uuid": "5fd813ce1b7342e38c0c576936e44720", "flavors": {"pytorch": {"model_data": "data", "pytorch_version": "2.5.1+cu124", "code": null}, "python_function": {"pickle_module_name": "mlflow.pytorch.pickle_module", "loader_module": "mlflow.pytorch", "python_version": "3.11.11", "data": "data", "env": {"conda": "conda.yaml", "virtualenv": "python_env.yaml"}}}}]</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
